--- a/通勤経路届（その他利用）2020.xlsx
+++ b/通勤経路届（その他利用）2020.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\trust.local\tech-fs\TECH\営業本部\EG関西-大阪\楢崎\エクセルデータ\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5873D2EE-1C6F-4716-B7A5-89C44B0450CD}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40920" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="通勤経路届(その他ﾌｫｰﾏｯﾄ)" sheetId="1" r:id="rId1"/>
@@ -18,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'通勤経路届(その他ﾌｫｰﾏｯﾄ)'!$A$1:$T$41</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <r>
       <rPr>
@@ -501,12 +495,112 @@
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
+  <si>
+    <t>日新電機株式会社</t>
+    <rPh sb="0" eb="2">
+      <t>ニッシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>デンキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガイシャ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>九条工場</t>
+    <rPh sb="0" eb="2">
+      <t>クジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>京都府京都市南区吉祥院三ノ宮町132</t>
+    <rPh sb="0" eb="3">
+      <t>キョウトフ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>キョウトシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ミナミク</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>キッショウイン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミヤ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>京都府京都市右京区太秦朱雀町1-10　レオパレス豊206号室</t>
+    <rPh sb="0" eb="3">
+      <t>キョウトフ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>キョウトシ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ウキョウク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ウズマサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スザク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>マチ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ユタカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ゴウシツ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>大阪オフィス</t>
+    <rPh sb="0" eb="2">
+      <t>オオサカ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>神崎　淳</t>
+    <rPh sb="0" eb="2">
+      <t>カンザキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジュン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>かんざき　じゅん</t>
+    <phoneticPr fontId="5"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -676,7 +770,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -1314,11 +1408,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -1741,6 +1846,12 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1765,7 +1876,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1773,7 +1884,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1785,7 +1896,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1820,14 +1931,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -1835,24 +1943,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -1882,14 +1972,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -1897,24 +1984,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -1944,14 +2013,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -1959,24 +2025,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -2006,14 +2054,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -2021,24 +2066,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -2068,14 +2095,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -2083,24 +2107,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -2130,14 +2136,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1030"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -2145,24 +2148,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -2192,14 +2177,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1031"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -2207,24 +2189,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -2254,14 +2218,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1032"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -2269,24 +2230,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -2316,14 +2259,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1033"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009040000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -2331,24 +2271,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="D8D8D8"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="12700">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -2356,6 +2278,44 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>83843</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>278724</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="83843" y="4343399"/>
+          <a:ext cx="3516607" cy="4755475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2614,22 +2574,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AE43"/>
-  <sheetFormatPr defaultColWidth="6.86328125" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.875" defaultRowHeight="19.5" customHeight="1"/>
   <cols>
-    <col min="1" max="20" width="4.59765625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="6.86328125" style="1"/>
+    <col min="1" max="20" width="4.625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="6.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="33">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -2653,7 +2613,7 @@
       <c r="S1" s="34"/>
       <c r="T1" s="34"/>
     </row>
-    <row r="2" spans="1:31" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="9.75" customHeight="1" thickBot="1">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2675,22 +2635,28 @@
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
     </row>
-    <row r="3" spans="1:31" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="16.5" customHeight="1">
       <c r="A3" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="36"/>
       <c r="C3" s="37"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="41"/>
+      <c r="D3" s="142">
+        <v>2020</v>
+      </c>
+      <c r="E3" s="36"/>
       <c r="F3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="41"/>
+      <c r="G3" s="41">
+        <v>4</v>
+      </c>
       <c r="H3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="41"/>
+      <c r="I3" s="41">
+        <v>1</v>
+      </c>
       <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
@@ -2700,25 +2666,31 @@
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="7"/>
+      <c r="O3" s="7">
+        <v>2020</v>
+      </c>
       <c r="P3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="7"/>
+      <c r="Q3" s="7">
+        <v>3</v>
+      </c>
       <c r="R3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S3" s="7"/>
+      <c r="S3" s="7">
+        <v>10</v>
+      </c>
       <c r="T3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="6" customHeight="1" thickBot="1">
       <c r="A4" s="38"/>
       <c r="B4" s="39"/>
       <c r="C4" s="40"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="42"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="39"/>
       <c r="G4" s="42"/>
       <c r="H4" s="39"/>
@@ -2735,13 +2707,15 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
     </row>
-    <row r="5" spans="1:31" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="16.5" customHeight="1">
       <c r="A5" s="35" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="36"/>
       <c r="C5" s="37"/>
-      <c r="D5" s="48"/>
+      <c r="D5" s="48">
+        <v>201087</v>
+      </c>
       <c r="E5" s="48"/>
       <c r="F5" s="48"/>
       <c r="G5" s="48"/>
@@ -2754,14 +2728,16 @@
       </c>
       <c r="M5" s="52"/>
       <c r="N5" s="52"/>
-      <c r="O5" s="53"/>
+      <c r="O5" s="53" t="s">
+        <v>49</v>
+      </c>
       <c r="P5" s="53"/>
       <c r="Q5" s="53"/>
       <c r="R5" s="53"/>
       <c r="S5" s="53"/>
       <c r="T5" s="53"/>
     </row>
-    <row r="6" spans="1:31" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="6.75" customHeight="1" thickBot="1">
       <c r="A6" s="45"/>
       <c r="B6" s="46"/>
       <c r="C6" s="47"/>
@@ -2783,7 +2759,7 @@
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
     </row>
-    <row r="7" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="18" customHeight="1">
       <c r="A7" s="54" t="s">
         <v>9</v>
       </c>
@@ -2811,12 +2787,14 @@
       <c r="S7" s="58"/>
       <c r="T7" s="60"/>
     </row>
-    <row r="8" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="19.5" customHeight="1">
       <c r="A8" s="83" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="84"/>
-      <c r="C8" s="85"/>
+      <c r="C8" s="85" t="s">
+        <v>51</v>
+      </c>
       <c r="D8" s="85"/>
       <c r="E8" s="85"/>
       <c r="F8" s="85"/>
@@ -2839,8 +2817,10 @@
       <c r="S8" s="63"/>
       <c r="T8" s="64"/>
     </row>
-    <row r="9" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
+    <row r="9" spans="1:31" ht="12" customHeight="1">
+      <c r="A9" s="65" t="s">
+        <v>50</v>
+      </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
       <c r="D9" s="66"/>
@@ -2861,7 +2841,7 @@
       <c r="S9" s="63"/>
       <c r="T9" s="64"/>
     </row>
-    <row r="10" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="12" customHeight="1">
       <c r="A10" s="65"/>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
@@ -2872,15 +2852,21 @@
       <c r="H10" s="66"/>
       <c r="I10" s="66"/>
       <c r="J10" s="67"/>
-      <c r="K10" s="71"/>
+      <c r="K10" s="71">
+        <v>5</v>
+      </c>
       <c r="L10" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="75"/>
+      <c r="M10" s="75">
+        <v>8</v>
+      </c>
       <c r="N10" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="75"/>
+      <c r="O10" s="75">
+        <v>24</v>
+      </c>
       <c r="P10" s="77" t="s">
         <v>5</v>
       </c>
@@ -2893,7 +2879,7 @@
       </c>
       <c r="T10" s="88"/>
     </row>
-    <row r="11" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="12" customHeight="1">
       <c r="A11" s="68"/>
       <c r="B11" s="69"/>
       <c r="C11" s="69"/>
@@ -2915,19 +2901,23 @@
       <c r="S11" s="89"/>
       <c r="T11" s="90"/>
     </row>
-    <row r="12" spans="1:31" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="91" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="93"/>
+      <c r="C12" s="93">
+        <v>616</v>
+      </c>
       <c r="D12" s="93"/>
       <c r="E12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="93"/>
+      <c r="F12" s="93">
+        <v>8137</v>
+      </c>
       <c r="G12" s="93"/>
       <c r="H12" s="15"/>
       <c r="I12" s="16"/>
@@ -2943,12 +2933,14 @@
       <c r="S12" s="16"/>
       <c r="T12" s="17"/>
     </row>
-    <row r="13" spans="1:31" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="27.95" customHeight="1">
       <c r="A13" s="92"/>
       <c r="B13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="94"/>
+      <c r="C13" s="94" t="s">
+        <v>48</v>
+      </c>
       <c r="D13" s="94"/>
       <c r="E13" s="94"/>
       <c r="F13" s="94"/>
@@ -2967,7 +2959,7 @@
       <c r="S13" s="94"/>
       <c r="T13" s="95"/>
     </row>
-    <row r="14" spans="1:31" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="27.95" customHeight="1">
       <c r="A14" s="110" t="s">
         <v>20</v>
       </c>
@@ -2975,7 +2967,9 @@
         <v>21</v>
       </c>
       <c r="C14" s="114"/>
-      <c r="D14" s="115"/>
+      <c r="D14" s="115" t="s">
+        <v>45</v>
+      </c>
       <c r="E14" s="116"/>
       <c r="F14" s="116"/>
       <c r="G14" s="116"/>
@@ -2986,7 +2980,9 @@
       </c>
       <c r="K14" s="117"/>
       <c r="L14" s="117"/>
-      <c r="M14" s="118"/>
+      <c r="M14" s="118" t="s">
+        <v>46</v>
+      </c>
       <c r="N14" s="119"/>
       <c r="O14" s="119"/>
       <c r="P14" s="119"/>
@@ -2996,17 +2992,21 @@
       <c r="T14" s="120"/>
       <c r="AE14" s="19"/>
     </row>
-    <row r="15" spans="1:31" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="17.100000000000001" customHeight="1">
       <c r="A15" s="111"/>
       <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="96"/>
+      <c r="C15" s="96">
+        <v>601</v>
+      </c>
       <c r="D15" s="96"/>
       <c r="E15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="96"/>
+      <c r="F15" s="96">
+        <v>8319</v>
+      </c>
       <c r="G15" s="96"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
@@ -3023,12 +3023,14 @@
       <c r="T15" s="21"/>
       <c r="AE15" s="19"/>
     </row>
-    <row r="16" spans="1:31" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" ht="27.95" customHeight="1" thickBot="1">
       <c r="A16" s="112"/>
       <c r="B16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="97"/>
+      <c r="C16" s="97" t="s">
+        <v>47</v>
+      </c>
       <c r="D16" s="97"/>
       <c r="E16" s="97"/>
       <c r="F16" s="97"/>
@@ -3047,7 +3049,7 @@
       <c r="S16" s="97"/>
       <c r="T16" s="98"/>
     </row>
-    <row r="17" spans="1:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="18.95" customHeight="1">
       <c r="A17" s="99" t="s">
         <v>25</v>
       </c>
@@ -3071,7 +3073,7 @@
       <c r="S17" s="101"/>
       <c r="T17" s="102"/>
     </row>
-    <row r="18" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="21.95" customHeight="1">
       <c r="A18" s="103" t="s">
         <v>26</v>
       </c>
@@ -3083,7 +3085,9 @@
       </c>
       <c r="F18" s="106"/>
       <c r="G18" s="107"/>
-      <c r="H18" s="108"/>
+      <c r="H18" s="108">
+        <v>5.2</v>
+      </c>
       <c r="I18" s="109"/>
       <c r="J18" s="23" t="s">
         <v>28</v>
@@ -3093,7 +3097,9 @@
       </c>
       <c r="L18" s="106"/>
       <c r="M18" s="107"/>
-      <c r="N18" s="108"/>
+      <c r="N18" s="108">
+        <v>10.4</v>
+      </c>
       <c r="O18" s="109"/>
       <c r="P18" s="23" t="s">
         <v>28</v>
@@ -3103,7 +3109,7 @@
       <c r="S18" s="24"/>
       <c r="T18" s="25"/>
     </row>
-    <row r="19" spans="1:20" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="23.1" customHeight="1">
       <c r="A19" s="137" t="s">
         <v>30</v>
       </c>
@@ -3137,7 +3143,7 @@
       <c r="S19" s="123"/>
       <c r="T19" s="136"/>
     </row>
-    <row r="20" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="24" customHeight="1">
       <c r="A20" s="125" t="s">
         <v>36</v>
       </c>
@@ -3161,7 +3167,7 @@
       <c r="S20" s="126"/>
       <c r="T20" s="127"/>
     </row>
-    <row r="21" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="24" customHeight="1">
       <c r="A21" s="128"/>
       <c r="B21" s="129"/>
       <c r="C21" s="129"/>
@@ -3183,7 +3189,7 @@
       <c r="S21" s="129"/>
       <c r="T21" s="130"/>
     </row>
-    <row r="22" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="24" customHeight="1">
       <c r="A22" s="128"/>
       <c r="B22" s="129"/>
       <c r="C22" s="129"/>
@@ -3205,7 +3211,7 @@
       <c r="S22" s="129"/>
       <c r="T22" s="130"/>
     </row>
-    <row r="23" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="24" customHeight="1">
       <c r="A23" s="128"/>
       <c r="B23" s="129"/>
       <c r="C23" s="129"/>
@@ -3227,7 +3233,7 @@
       <c r="S23" s="129"/>
       <c r="T23" s="130"/>
     </row>
-    <row r="24" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="21.95" customHeight="1">
       <c r="A24" s="128"/>
       <c r="B24" s="129"/>
       <c r="C24" s="129"/>
@@ -3249,7 +3255,7 @@
       <c r="S24" s="129"/>
       <c r="T24" s="130"/>
     </row>
-    <row r="25" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="21.95" customHeight="1">
       <c r="A25" s="128"/>
       <c r="B25" s="129"/>
       <c r="C25" s="129"/>
@@ -3271,7 +3277,7 @@
       <c r="S25" s="129"/>
       <c r="T25" s="130"/>
     </row>
-    <row r="26" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="21.95" customHeight="1">
       <c r="A26" s="128"/>
       <c r="B26" s="129"/>
       <c r="C26" s="129"/>
@@ -3293,7 +3299,7 @@
       <c r="S26" s="129"/>
       <c r="T26" s="130"/>
     </row>
-    <row r="27" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="24" customHeight="1">
       <c r="A27" s="131"/>
       <c r="B27" s="129"/>
       <c r="C27" s="129"/>
@@ -3315,7 +3321,7 @@
       <c r="S27" s="129"/>
       <c r="T27" s="130"/>
     </row>
-    <row r="28" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="24" customHeight="1">
       <c r="A28" s="128"/>
       <c r="B28" s="129"/>
       <c r="C28" s="129"/>
@@ -3337,7 +3343,7 @@
       <c r="S28" s="129"/>
       <c r="T28" s="130"/>
     </row>
-    <row r="29" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="24" customHeight="1">
       <c r="A29" s="128"/>
       <c r="B29" s="129"/>
       <c r="C29" s="129"/>
@@ -3359,7 +3365,7 @@
       <c r="S29" s="129"/>
       <c r="T29" s="130"/>
     </row>
-    <row r="30" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="24" customHeight="1">
       <c r="A30" s="128"/>
       <c r="B30" s="129"/>
       <c r="C30" s="129"/>
@@ -3381,7 +3387,7 @@
       <c r="S30" s="129"/>
       <c r="T30" s="130"/>
     </row>
-    <row r="31" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="24" customHeight="1">
       <c r="A31" s="128"/>
       <c r="B31" s="129"/>
       <c r="C31" s="129"/>
@@ -3403,7 +3409,7 @@
       <c r="S31" s="129"/>
       <c r="T31" s="130"/>
     </row>
-    <row r="32" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="24" customHeight="1">
       <c r="A32" s="128"/>
       <c r="B32" s="129"/>
       <c r="C32" s="129"/>
@@ -3425,7 +3431,7 @@
       <c r="S32" s="129"/>
       <c r="T32" s="130"/>
     </row>
-    <row r="33" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="24" customHeight="1">
       <c r="A33" s="128"/>
       <c r="B33" s="129"/>
       <c r="C33" s="129"/>
@@ -3447,7 +3453,7 @@
       <c r="S33" s="129"/>
       <c r="T33" s="130"/>
     </row>
-    <row r="34" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="24" customHeight="1">
       <c r="A34" s="128"/>
       <c r="B34" s="129"/>
       <c r="C34" s="129"/>
@@ -3469,7 +3475,7 @@
       <c r="S34" s="129"/>
       <c r="T34" s="130"/>
     </row>
-    <row r="35" spans="1:20" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" ht="24" customHeight="1" thickBot="1">
       <c r="A35" s="133"/>
       <c r="B35" s="134"/>
       <c r="C35" s="134"/>
@@ -3491,7 +3497,7 @@
       <c r="S35" s="134"/>
       <c r="T35" s="135"/>
     </row>
-    <row r="36" spans="1:20" ht="5.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:20" ht="5.25" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -3513,7 +3519,7 @@
       <c r="S36" s="27"/>
       <c r="T36" s="27"/>
     </row>
-    <row r="37" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="18" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>37</v>
       </c>
@@ -3541,7 +3547,7 @@
       <c r="S37" s="139"/>
       <c r="T37" s="140"/>
     </row>
-    <row r="38" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="18" customHeight="1">
       <c r="A38" s="28" t="s">
         <v>40</v>
       </c>
@@ -3565,7 +3571,7 @@
       <c r="S38" s="141"/>
       <c r="T38" s="141"/>
     </row>
-    <row r="39" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="18" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -3589,7 +3595,7 @@
       <c r="S39" s="141"/>
       <c r="T39" s="141"/>
     </row>
-    <row r="40" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="18" customHeight="1">
       <c r="A40" s="28" t="s">
         <v>42</v>
       </c>
@@ -3613,7 +3619,7 @@
       <c r="S40" s="141"/>
       <c r="T40" s="141"/>
     </row>
-    <row r="41" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:20" ht="18" customHeight="1">
       <c r="A41" s="29" t="s">
         <v>43</v>
       </c>
@@ -3639,7 +3645,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="19.5" customHeight="1">
       <c r="A42" s="32"/>
       <c r="B42" s="32"/>
       <c r="C42" s="32"/>
@@ -3661,13 +3667,13 @@
       <c r="S42" s="32"/>
       <c r="T42" s="32"/>
     </row>
-    <row r="43" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="19.5" customHeight="1">
       <c r="J43" s="32"/>
       <c r="K43" s="32"/>
       <c r="L43" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="62">
     <mergeCell ref="L37:Q37"/>
     <mergeCell ref="R37:T37"/>
     <mergeCell ref="L38:N40"/>
@@ -3724,13 +3730,12 @@
     <mergeCell ref="Q7:T7"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D3:E4"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/通勤経路届（その他利用）2020.xlsx
+++ b/通勤経路届（その他利用）2020.xlsx
@@ -1521,10 +1521,247 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1534,27 +1771,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1605,247 +1821,31 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2574,7 +2574,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2590,28 +2590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="33">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
     </row>
     <row r="2" spans="1:31" ht="9.75" customHeight="1" thickBot="1">
       <c r="A2" s="2"/>
@@ -2636,28 +2636,28 @@
       <c r="T2" s="3"/>
     </row>
     <row r="3" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="116"/>
       <c r="D3" s="142">
         <v>2020</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="115"/>
+      <c r="F3" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="138">
         <v>4</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="138">
         <v>1</v>
       </c>
-      <c r="J3" s="43" t="s">
+      <c r="J3" s="140" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="3"/>
@@ -2679,23 +2679,23 @@
         <v>4</v>
       </c>
       <c r="S3" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="6" customHeight="1" thickBot="1">
-      <c r="A4" s="38"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="137"/>
       <c r="D4" s="143"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="44"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="141"/>
       <c r="K4" s="3"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -2708,46 +2708,46 @@
       <c r="T4" s="3"/>
     </row>
     <row r="5" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="48">
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="120">
         <v>201087</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="49"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="53" t="s">
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="53"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="125"/>
     </row>
     <row r="6" spans="1:31" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="51"/>
+      <c r="A6" s="117"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="123"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="10"/>
@@ -2760,165 +2760,165 @@
       <c r="T6" s="9"/>
     </row>
     <row r="7" spans="1:31" ht="18" customHeight="1">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="57" t="s">
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="129" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="57" t="s">
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="129" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="60"/>
+      <c r="R7" s="130"/>
+      <c r="S7" s="130"/>
+      <c r="T7" s="132"/>
     </row>
     <row r="8" spans="1:31" ht="19.5" customHeight="1">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="85" t="s">
+      <c r="B8" s="111"/>
+      <c r="C8" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="63" t="s">
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="90" t="s">
         <v>13</v>
       </c>
       <c r="M8" s="3"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63" t="s">
+      <c r="N8" s="90"/>
+      <c r="O8" s="90" t="s">
         <v>2</v>
       </c>
       <c r="P8" s="12"/>
-      <c r="Q8" s="61"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="64"/>
+      <c r="Q8" s="89"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="91"/>
     </row>
     <row r="9" spans="1:31" ht="12" customHeight="1">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="63"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="90"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="90"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="62"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="64"/>
+      <c r="Q9" s="89"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="91"/>
     </row>
     <row r="10" spans="1:31" ht="12" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="71">
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="98">
         <v>5</v>
       </c>
-      <c r="L10" s="73" t="s">
+      <c r="L10" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="75">
+      <c r="M10" s="102">
         <v>8</v>
       </c>
-      <c r="N10" s="73" t="s">
+      <c r="N10" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="75">
+      <c r="O10" s="102">
         <v>24</v>
       </c>
-      <c r="P10" s="77" t="s">
+      <c r="P10" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="79" t="s">
+      <c r="Q10" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="80"/>
-      <c r="S10" s="87" t="s">
+      <c r="R10" s="107"/>
+      <c r="S10" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="88"/>
+      <c r="T10" s="81"/>
     </row>
     <row r="11" spans="1:31" ht="12" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="82"/>
-      <c r="S11" s="89"/>
-      <c r="T11" s="90"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="105"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="83"/>
     </row>
     <row r="12" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="84" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="93">
+      <c r="C12" s="86">
         <v>616</v>
       </c>
-      <c r="D12" s="93"/>
+      <c r="D12" s="86"/>
       <c r="E12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="93">
+      <c r="F12" s="86">
         <v>8137</v>
       </c>
-      <c r="G12" s="93"/>
+      <c r="G12" s="86"/>
       <c r="H12" s="15"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -2934,80 +2934,80 @@
       <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A13" s="92"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
-      <c r="S13" s="94"/>
-      <c r="T13" s="95"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="87"/>
+      <c r="M13" s="87"/>
+      <c r="N13" s="87"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="88"/>
     </row>
     <row r="14" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="113" t="s">
+      <c r="B14" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="114"/>
-      <c r="D14" s="115" t="s">
+      <c r="C14" s="73"/>
+      <c r="D14" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="113" t="s">
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="117"/>
-      <c r="L14" s="117"/>
-      <c r="M14" s="118" t="s">
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="119"/>
-      <c r="O14" s="119"/>
-      <c r="P14" s="119"/>
-      <c r="Q14" s="119"/>
-      <c r="R14" s="119"/>
-      <c r="S14" s="119"/>
-      <c r="T14" s="120"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="79"/>
       <c r="AE14" s="19"/>
     </row>
     <row r="15" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A15" s="111"/>
+      <c r="A15" s="70"/>
       <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="96">
+      <c r="C15" s="55">
         <v>601</v>
       </c>
-      <c r="D15" s="96"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="96">
+      <c r="F15" s="55">
         <v>8319</v>
       </c>
-      <c r="G15" s="96"/>
+      <c r="G15" s="55"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -3024,83 +3024,83 @@
       <c r="AE15" s="19"/>
     </row>
     <row r="16" spans="1:31" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A16" s="112"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="97" t="s">
+      <c r="C16" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="97"/>
-      <c r="E16" s="97"/>
-      <c r="F16" s="97"/>
-      <c r="G16" s="97"/>
-      <c r="H16" s="97"/>
-      <c r="I16" s="97"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="97"/>
-      <c r="M16" s="97"/>
-      <c r="N16" s="97"/>
-      <c r="O16" s="97"/>
-      <c r="P16" s="97"/>
-      <c r="Q16" s="97"/>
-      <c r="R16" s="97"/>
-      <c r="S16" s="97"/>
-      <c r="T16" s="98"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="57"/>
     </row>
     <row r="17" spans="1:20" ht="18.95" customHeight="1">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="100"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="101"/>
-      <c r="P17" s="101"/>
-      <c r="Q17" s="101"/>
-      <c r="R17" s="101"/>
-      <c r="S17" s="101"/>
-      <c r="T17" s="102"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="61"/>
     </row>
     <row r="18" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="105" t="s">
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="106"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="108">
+      <c r="F18" s="65"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="67">
         <v>5.2</v>
       </c>
-      <c r="I18" s="109"/>
+      <c r="I18" s="68"/>
       <c r="J18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="105" t="s">
+      <c r="K18" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="106"/>
-      <c r="M18" s="107"/>
-      <c r="N18" s="108">
+      <c r="L18" s="65"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="67">
         <v>10.4</v>
       </c>
-      <c r="O18" s="109"/>
+      <c r="O18" s="68"/>
       <c r="P18" s="23" t="s">
         <v>28</v>
       </c>
@@ -3110,392 +3110,392 @@
       <c r="T18" s="25"/>
     </row>
     <row r="19" spans="1:20" ht="23.1" customHeight="1">
-      <c r="A19" s="137" t="s">
+      <c r="A19" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="62"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="26"/>
-      <c r="D19" s="121" t="s">
+      <c r="D19" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="121"/>
-      <c r="F19" s="122"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
       <c r="G19" s="26"/>
-      <c r="H19" s="121" t="s">
+      <c r="H19" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="121"/>
-      <c r="J19" s="122"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="38"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="123" t="s">
+      <c r="L19" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="123"/>
+      <c r="M19" s="39"/>
       <c r="N19" s="26"/>
-      <c r="O19" s="123" t="s">
+      <c r="O19" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="P19" s="124"/>
+      <c r="P19" s="40"/>
       <c r="Q19" s="9"/>
-      <c r="R19" s="123" t="s">
+      <c r="R19" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="S19" s="123"/>
-      <c r="T19" s="136"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="52"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="126"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="126"/>
-      <c r="Q20" s="126"/>
-      <c r="R20" s="126"/>
-      <c r="S20" s="126"/>
-      <c r="T20" s="127"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="43"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1">
-      <c r="A21" s="128"/>
-      <c r="B21" s="129"/>
-      <c r="C21" s="129"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="129"/>
-      <c r="K21" s="129"/>
-      <c r="L21" s="129"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="129"/>
-      <c r="O21" s="129"/>
-      <c r="P21" s="129"/>
-      <c r="Q21" s="129"/>
-      <c r="R21" s="129"/>
-      <c r="S21" s="129"/>
-      <c r="T21" s="130"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="46"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1">
-      <c r="A22" s="128"/>
-      <c r="B22" s="129"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="129"/>
-      <c r="H22" s="129"/>
-      <c r="I22" s="129"/>
-      <c r="J22" s="129"/>
-      <c r="K22" s="129"/>
-      <c r="L22" s="129"/>
-      <c r="M22" s="129"/>
-      <c r="N22" s="129"/>
-      <c r="O22" s="129"/>
-      <c r="P22" s="129"/>
-      <c r="Q22" s="129"/>
-      <c r="R22" s="129"/>
-      <c r="S22" s="129"/>
-      <c r="T22" s="130"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="45"/>
+      <c r="S22" s="45"/>
+      <c r="T22" s="46"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1">
-      <c r="A23" s="128"/>
-      <c r="B23" s="129"/>
-      <c r="C23" s="129"/>
-      <c r="D23" s="129"/>
-      <c r="E23" s="129"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="129"/>
-      <c r="K23" s="129"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="129"/>
-      <c r="Q23" s="129"/>
-      <c r="R23" s="129"/>
-      <c r="S23" s="129"/>
-      <c r="T23" s="130"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="46"/>
     </row>
     <row r="24" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A24" s="128"/>
-      <c r="B24" s="129"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="129"/>
-      <c r="K24" s="129"/>
-      <c r="L24" s="129"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="129"/>
-      <c r="O24" s="129"/>
-      <c r="P24" s="129"/>
-      <c r="Q24" s="129"/>
-      <c r="R24" s="129"/>
-      <c r="S24" s="129"/>
-      <c r="T24" s="130"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="46"/>
     </row>
     <row r="25" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A25" s="128"/>
-      <c r="B25" s="129"/>
-      <c r="C25" s="129"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="129"/>
-      <c r="H25" s="129"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="129"/>
-      <c r="K25" s="129"/>
-      <c r="L25" s="129"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="129"/>
-      <c r="O25" s="129"/>
-      <c r="P25" s="129"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="129"/>
-      <c r="S25" s="129"/>
-      <c r="T25" s="130"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="45"/>
+      <c r="R25" s="45"/>
+      <c r="S25" s="45"/>
+      <c r="T25" s="46"/>
     </row>
     <row r="26" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A26" s="128"/>
-      <c r="B26" s="129"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="129"/>
-      <c r="E26" s="129"/>
-      <c r="F26" s="129"/>
-      <c r="G26" s="129"/>
-      <c r="H26" s="129"/>
-      <c r="I26" s="129"/>
-      <c r="J26" s="129"/>
-      <c r="K26" s="129"/>
-      <c r="L26" s="129"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="129"/>
-      <c r="P26" s="129"/>
-      <c r="Q26" s="129"/>
-      <c r="R26" s="129"/>
-      <c r="S26" s="129"/>
-      <c r="T26" s="130"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="46"/>
     </row>
     <row r="27" spans="1:20" ht="24" customHeight="1">
-      <c r="A27" s="131"/>
-      <c r="B27" s="129"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="129"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="129"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="129"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="129"/>
-      <c r="O27" s="129"/>
-      <c r="P27" s="129"/>
-      <c r="Q27" s="129"/>
-      <c r="R27" s="129"/>
-      <c r="S27" s="129"/>
-      <c r="T27" s="130"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="45"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="46"/>
     </row>
     <row r="28" spans="1:20" ht="24" customHeight="1">
-      <c r="A28" s="128"/>
-      <c r="B28" s="129"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="129"/>
-      <c r="K28" s="129"/>
-      <c r="L28" s="129"/>
-      <c r="M28" s="129"/>
-      <c r="N28" s="129"/>
-      <c r="O28" s="129"/>
-      <c r="P28" s="129"/>
-      <c r="Q28" s="129"/>
-      <c r="R28" s="129"/>
-      <c r="S28" s="129"/>
-      <c r="T28" s="130"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="46"/>
     </row>
     <row r="29" spans="1:20" ht="24" customHeight="1">
-      <c r="A29" s="128"/>
-      <c r="B29" s="129"/>
-      <c r="C29" s="129"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="129"/>
-      <c r="J29" s="129"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="129"/>
-      <c r="M29" s="129"/>
-      <c r="N29" s="129"/>
-      <c r="O29" s="129"/>
-      <c r="P29" s="129"/>
-      <c r="Q29" s="129"/>
-      <c r="R29" s="129"/>
-      <c r="S29" s="129"/>
-      <c r="T29" s="130"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="45"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="45"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="46"/>
     </row>
     <row r="30" spans="1:20" ht="24" customHeight="1">
-      <c r="A30" s="128"/>
-      <c r="B30" s="129"/>
-      <c r="C30" s="129"/>
-      <c r="D30" s="129"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="129"/>
-      <c r="J30" s="129"/>
-      <c r="K30" s="129"/>
-      <c r="L30" s="129"/>
-      <c r="M30" s="129"/>
-      <c r="N30" s="129"/>
-      <c r="O30" s="129"/>
-      <c r="P30" s="129"/>
-      <c r="Q30" s="129"/>
-      <c r="R30" s="129"/>
-      <c r="S30" s="129"/>
-      <c r="T30" s="130"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="46"/>
     </row>
     <row r="31" spans="1:20" ht="24" customHeight="1">
-      <c r="A31" s="128"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="129"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="129"/>
-      <c r="G31" s="129"/>
-      <c r="H31" s="129"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="129"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="129"/>
-      <c r="M31" s="129"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="129"/>
-      <c r="P31" s="129"/>
-      <c r="Q31" s="129"/>
-      <c r="R31" s="129"/>
-      <c r="S31" s="129"/>
-      <c r="T31" s="130"/>
+      <c r="A31" s="44"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="45"/>
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="46"/>
     </row>
     <row r="32" spans="1:20" ht="24" customHeight="1">
-      <c r="A32" s="128"/>
-      <c r="B32" s="129"/>
-      <c r="C32" s="129"/>
-      <c r="D32" s="129"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="129"/>
-      <c r="G32" s="129"/>
-      <c r="H32" s="129"/>
-      <c r="I32" s="129"/>
-      <c r="J32" s="129"/>
-      <c r="K32" s="129"/>
-      <c r="L32" s="129"/>
-      <c r="M32" s="129"/>
-      <c r="N32" s="129"/>
-      <c r="O32" s="129"/>
-      <c r="P32" s="129"/>
-      <c r="Q32" s="129"/>
-      <c r="R32" s="129"/>
-      <c r="S32" s="129"/>
-      <c r="T32" s="130"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="45"/>
+      <c r="P32" s="45"/>
+      <c r="Q32" s="45"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="46"/>
     </row>
     <row r="33" spans="1:20" ht="24" customHeight="1">
-      <c r="A33" s="128"/>
-      <c r="B33" s="129"/>
-      <c r="C33" s="129"/>
-      <c r="D33" s="129"/>
-      <c r="E33" s="129"/>
-      <c r="F33" s="129"/>
-      <c r="G33" s="129"/>
-      <c r="H33" s="129"/>
-      <c r="I33" s="129"/>
-      <c r="J33" s="129"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="129"/>
-      <c r="M33" s="129"/>
-      <c r="N33" s="129"/>
-      <c r="O33" s="129"/>
-      <c r="P33" s="129"/>
-      <c r="Q33" s="129"/>
-      <c r="R33" s="129"/>
-      <c r="S33" s="129"/>
-      <c r="T33" s="130"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="45"/>
+      <c r="P33" s="45"/>
+      <c r="Q33" s="45"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="46"/>
     </row>
     <row r="34" spans="1:20" ht="24" customHeight="1">
-      <c r="A34" s="128"/>
-      <c r="B34" s="129"/>
-      <c r="C34" s="129"/>
-      <c r="D34" s="129"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="129"/>
-      <c r="G34" s="129"/>
-      <c r="H34" s="129"/>
-      <c r="I34" s="129"/>
-      <c r="J34" s="129"/>
-      <c r="K34" s="129"/>
-      <c r="L34" s="129"/>
-      <c r="M34" s="129"/>
-      <c r="N34" s="129"/>
-      <c r="O34" s="129"/>
-      <c r="P34" s="129"/>
-      <c r="Q34" s="129"/>
-      <c r="R34" s="129"/>
-      <c r="S34" s="129"/>
-      <c r="T34" s="130"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="45"/>
+      <c r="P34" s="45"/>
+      <c r="Q34" s="45"/>
+      <c r="R34" s="45"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="46"/>
     </row>
     <row r="35" spans="1:20" ht="24" customHeight="1" thickBot="1">
-      <c r="A35" s="133"/>
-      <c r="B35" s="134"/>
-      <c r="C35" s="134"/>
-      <c r="D35" s="134"/>
-      <c r="E35" s="134"/>
-      <c r="F35" s="134"/>
-      <c r="G35" s="134"/>
-      <c r="H35" s="134"/>
-      <c r="I35" s="134"/>
-      <c r="J35" s="134"/>
-      <c r="K35" s="134"/>
-      <c r="L35" s="134"/>
-      <c r="M35" s="134"/>
-      <c r="N35" s="134"/>
-      <c r="O35" s="134"/>
-      <c r="P35" s="134"/>
-      <c r="Q35" s="134"/>
-      <c r="R35" s="134"/>
-      <c r="S35" s="134"/>
-      <c r="T35" s="135"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="50"/>
+      <c r="T35" s="51"/>
     </row>
     <row r="36" spans="1:20" ht="5.25" customHeight="1">
       <c r="A36" s="3"/>
@@ -3533,19 +3533,19 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
-      <c r="L37" s="138" t="s">
+      <c r="L37" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="139"/>
-      <c r="N37" s="139"/>
-      <c r="O37" s="139"/>
-      <c r="P37" s="139"/>
-      <c r="Q37" s="140"/>
-      <c r="R37" s="138" t="s">
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="S37" s="139"/>
-      <c r="T37" s="140"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="35"/>
     </row>
     <row r="38" spans="1:20" ht="18" customHeight="1">
       <c r="A38" s="28" t="s">
@@ -3561,15 +3561,15 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="141"/>
-      <c r="M38" s="141"/>
-      <c r="N38" s="141"/>
-      <c r="O38" s="141"/>
-      <c r="P38" s="141"/>
-      <c r="Q38" s="141"/>
-      <c r="R38" s="141"/>
-      <c r="S38" s="141"/>
-      <c r="T38" s="141"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
     </row>
     <row r="39" spans="1:20" ht="18" customHeight="1">
       <c r="A39" s="4" t="s">
@@ -3585,15 +3585,15 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="141"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="141"/>
-      <c r="P39" s="141"/>
-      <c r="Q39" s="141"/>
-      <c r="R39" s="141"/>
-      <c r="S39" s="141"/>
-      <c r="T39" s="141"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
     </row>
     <row r="40" spans="1:20" ht="18" customHeight="1">
       <c r="A40" s="28" t="s">
@@ -3609,15 +3609,15 @@
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
-      <c r="L40" s="141"/>
-      <c r="M40" s="141"/>
-      <c r="N40" s="141"/>
-      <c r="O40" s="141"/>
-      <c r="P40" s="141"/>
-      <c r="Q40" s="141"/>
-      <c r="R40" s="141"/>
-      <c r="S40" s="141"/>
-      <c r="T40" s="141"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
     </row>
     <row r="41" spans="1:20" ht="18" customHeight="1">
       <c r="A41" s="29" t="s">
@@ -3674,37 +3674,21 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="L37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="L38:N40"/>
-    <mergeCell ref="O38:Q40"/>
-    <mergeCell ref="R38:T40"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A20:T35"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C16:T16"/>
-    <mergeCell ref="A17:T17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:T14"/>
-    <mergeCell ref="S10:T11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C13:T13"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D3:E4"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:J6"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="Q7:T7"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="S8:T9"/>
     <mergeCell ref="A9:J11"/>
@@ -3721,21 +3705,37 @@
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="D5:J6"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="D3:E4"/>
+    <mergeCell ref="S10:T11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C13:T13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C16:T16"/>
+    <mergeCell ref="A17:T17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:T14"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A20:T35"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="L37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="L38:N40"/>
+    <mergeCell ref="O38:Q40"/>
+    <mergeCell ref="R38:T40"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/通勤経路届（その他利用）2020.xlsx
+++ b/通勤経路届（その他利用）2020.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="40920" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
@@ -1521,17 +1521,275 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -1584,274 +1842,16 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -2574,7 +2574,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2582,6 +2582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AE43"/>
   <sheetFormatPr defaultColWidth="6.875" defaultRowHeight="19.5" customHeight="1"/>
   <cols>
@@ -2590,28 +2591,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="33">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
     </row>
     <row r="2" spans="1:31" ht="9.75" customHeight="1" thickBot="1">
       <c r="A2" s="2"/>
@@ -2636,28 +2637,28 @@
       <c r="T2" s="3"/>
     </row>
     <row r="3" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A3" s="114" t="s">
+      <c r="A3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="142">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="45">
         <v>2020</v>
       </c>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="138">
+      <c r="G3" s="41">
         <v>4</v>
       </c>
-      <c r="H3" s="115" t="s">
+      <c r="H3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="138">
+      <c r="I3" s="41">
         <v>1</v>
       </c>
-      <c r="J3" s="140" t="s">
+      <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="3"/>
@@ -2679,23 +2680,23 @@
         <v>4</v>
       </c>
       <c r="S3" s="7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="6" customHeight="1" thickBot="1">
-      <c r="A4" s="135"/>
-      <c r="B4" s="136"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="141"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="3"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -2708,46 +2709,46 @@
       <c r="T4" s="3"/>
     </row>
     <row r="5" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="120">
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="50">
         <v>201087</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="124" t="s">
+      <c r="L5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="125" t="s">
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="125"/>
-      <c r="Q5" s="125"/>
-      <c r="R5" s="125"/>
-      <c r="S5" s="125"/>
-      <c r="T5" s="125"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
     </row>
     <row r="6" spans="1:31" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A6" s="117"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="10"/>
@@ -2760,165 +2761,165 @@
       <c r="T6" s="9"/>
     </row>
     <row r="7" spans="1:31" ht="18" customHeight="1">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="129" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="129" t="s">
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="60"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="132"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="60"/>
+      <c r="T7" s="62"/>
     </row>
     <row r="8" spans="1:31" ht="19.5" customHeight="1">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="112" t="s">
+      <c r="B8" s="86"/>
+      <c r="C8" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="90" t="s">
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="65" t="s">
         <v>13</v>
       </c>
       <c r="M8" s="3"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90" t="s">
+      <c r="N8" s="65"/>
+      <c r="O8" s="65" t="s">
         <v>2</v>
       </c>
       <c r="P8" s="12"/>
-      <c r="Q8" s="89"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="91"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="66"/>
     </row>
     <row r="9" spans="1:31" ht="12" customHeight="1">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="65"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="89"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="91"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="64"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:31" ht="12" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="98">
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="73">
         <v>5</v>
       </c>
-      <c r="L10" s="100" t="s">
+      <c r="L10" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="102">
+      <c r="M10" s="77">
         <v>8</v>
       </c>
-      <c r="N10" s="100" t="s">
+      <c r="N10" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="102">
+      <c r="O10" s="77">
         <v>24</v>
       </c>
-      <c r="P10" s="104" t="s">
+      <c r="P10" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="106" t="s">
+      <c r="Q10" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="107"/>
-      <c r="S10" s="80" t="s">
+      <c r="R10" s="82"/>
+      <c r="S10" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="81"/>
+      <c r="T10" s="90"/>
     </row>
     <row r="11" spans="1:31" ht="12" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="101"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="101"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="109"/>
-      <c r="S11" s="82"/>
-      <c r="T11" s="83"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="76"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="91"/>
+      <c r="T11" s="92"/>
     </row>
     <row r="12" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="93" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="95">
         <v>616</v>
       </c>
-      <c r="D12" s="86"/>
+      <c r="D12" s="95"/>
       <c r="E12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="86">
+      <c r="F12" s="95">
         <v>8137</v>
       </c>
-      <c r="G12" s="86"/>
+      <c r="G12" s="95"/>
       <c r="H12" s="15"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -2934,80 +2935,80 @@
       <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A13" s="85"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="87"/>
-      <c r="L13" s="87"/>
-      <c r="M13" s="87"/>
-      <c r="N13" s="87"/>
-      <c r="O13" s="87"/>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="87"/>
-      <c r="S13" s="87"/>
-      <c r="T13" s="88"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="96"/>
+      <c r="T13" s="97"/>
     </row>
     <row r="14" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74" t="s">
+      <c r="C14" s="116"/>
+      <c r="D14" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="72" t="s">
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="77" t="s">
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="79"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="121"/>
+      <c r="R14" s="121"/>
+      <c r="S14" s="121"/>
+      <c r="T14" s="122"/>
       <c r="AE14" s="19"/>
     </row>
     <row r="15" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A15" s="70"/>
+      <c r="A15" s="113"/>
       <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="98">
         <v>601</v>
       </c>
-      <c r="D15" s="55"/>
+      <c r="D15" s="98"/>
       <c r="E15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="98">
         <v>8319</v>
       </c>
-      <c r="G15" s="55"/>
+      <c r="G15" s="98"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -3024,83 +3025,83 @@
       <c r="AE15" s="19"/>
     </row>
     <row r="16" spans="1:31" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A16" s="71"/>
+      <c r="A16" s="114"/>
       <c r="B16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="56"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="56"/>
-      <c r="T16" s="57"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="99"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="100"/>
     </row>
     <row r="17" spans="1:20" ht="18.95" customHeight="1">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="61"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="102"/>
+      <c r="L17" s="102"/>
+      <c r="M17" s="102"/>
+      <c r="N17" s="102"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="103"/>
+      <c r="Q17" s="103"/>
+      <c r="R17" s="103"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="104"/>
     </row>
     <row r="18" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="64" t="s">
+      <c r="B18" s="106"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="67">
+      <c r="F18" s="108"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="110">
         <v>5.2</v>
       </c>
-      <c r="I18" s="68"/>
+      <c r="I18" s="111"/>
       <c r="J18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="64" t="s">
+      <c r="K18" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="65"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="67">
+      <c r="L18" s="108"/>
+      <c r="M18" s="109"/>
+      <c r="N18" s="110">
         <v>10.4</v>
       </c>
-      <c r="O18" s="68"/>
+      <c r="O18" s="111"/>
       <c r="P18" s="23" t="s">
         <v>28</v>
       </c>
@@ -3110,392 +3111,392 @@
       <c r="T18" s="25"/>
     </row>
     <row r="19" spans="1:20" ht="23.1" customHeight="1">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="139" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="54"/>
+      <c r="B19" s="64"/>
       <c r="C19" s="26"/>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="38"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="124"/>
       <c r="G19" s="26"/>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="37"/>
-      <c r="J19" s="38"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="124"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="125"/>
       <c r="N19" s="26"/>
-      <c r="O19" s="39" t="s">
+      <c r="O19" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="P19" s="40"/>
+      <c r="P19" s="126"/>
       <c r="Q19" s="9"/>
-      <c r="R19" s="39" t="s">
+      <c r="R19" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="S19" s="39"/>
-      <c r="T19" s="52"/>
+      <c r="S19" s="125"/>
+      <c r="T19" s="138"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="43"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="128"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="128"/>
+      <c r="O20" s="128"/>
+      <c r="P20" s="128"/>
+      <c r="Q20" s="128"/>
+      <c r="R20" s="128"/>
+      <c r="S20" s="128"/>
+      <c r="T20" s="129"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="46"/>
+      <c r="A21" s="130"/>
+      <c r="B21" s="131"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="131"/>
+      <c r="T21" s="132"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1">
-      <c r="A22" s="44"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="46"/>
+      <c r="A22" s="130"/>
+      <c r="B22" s="131"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
+      <c r="M22" s="131"/>
+      <c r="N22" s="131"/>
+      <c r="O22" s="131"/>
+      <c r="P22" s="131"/>
+      <c r="Q22" s="131"/>
+      <c r="R22" s="131"/>
+      <c r="S22" s="131"/>
+      <c r="T22" s="132"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="46"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="131"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="131"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
+      <c r="M23" s="131"/>
+      <c r="N23" s="131"/>
+      <c r="O23" s="131"/>
+      <c r="P23" s="131"/>
+      <c r="Q23" s="131"/>
+      <c r="R23" s="131"/>
+      <c r="S23" s="131"/>
+      <c r="T23" s="132"/>
     </row>
     <row r="24" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="46"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="131"/>
+      <c r="Q24" s="131"/>
+      <c r="R24" s="131"/>
+      <c r="S24" s="131"/>
+      <c r="T24" s="132"/>
     </row>
     <row r="25" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="46"/>
+      <c r="A25" s="130"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="131"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="131"/>
+      <c r="L25" s="131"/>
+      <c r="M25" s="131"/>
+      <c r="N25" s="131"/>
+      <c r="O25" s="131"/>
+      <c r="P25" s="131"/>
+      <c r="Q25" s="131"/>
+      <c r="R25" s="131"/>
+      <c r="S25" s="131"/>
+      <c r="T25" s="132"/>
     </row>
     <row r="26" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="46"/>
+      <c r="A26" s="130"/>
+      <c r="B26" s="131"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="131"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="131"/>
+      <c r="L26" s="131"/>
+      <c r="M26" s="131"/>
+      <c r="N26" s="131"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="131"/>
+      <c r="Q26" s="131"/>
+      <c r="R26" s="131"/>
+      <c r="S26" s="131"/>
+      <c r="T26" s="132"/>
     </row>
     <row r="27" spans="1:20" ht="24" customHeight="1">
-      <c r="A27" s="47"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="46"/>
+      <c r="A27" s="133"/>
+      <c r="B27" s="131"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="134"/>
+      <c r="L27" s="131"/>
+      <c r="M27" s="131"/>
+      <c r="N27" s="131"/>
+      <c r="O27" s="131"/>
+      <c r="P27" s="131"/>
+      <c r="Q27" s="131"/>
+      <c r="R27" s="131"/>
+      <c r="S27" s="131"/>
+      <c r="T27" s="132"/>
     </row>
     <row r="28" spans="1:20" ht="24" customHeight="1">
-      <c r="A28" s="44"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="46"/>
+      <c r="A28" s="130"/>
+      <c r="B28" s="131"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="131"/>
+      <c r="N28" s="131"/>
+      <c r="O28" s="131"/>
+      <c r="P28" s="131"/>
+      <c r="Q28" s="131"/>
+      <c r="R28" s="131"/>
+      <c r="S28" s="131"/>
+      <c r="T28" s="132"/>
     </row>
     <row r="29" spans="1:20" ht="24" customHeight="1">
-      <c r="A29" s="44"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="46"/>
+      <c r="A29" s="130"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
+      <c r="L29" s="131"/>
+      <c r="M29" s="131"/>
+      <c r="N29" s="131"/>
+      <c r="O29" s="131"/>
+      <c r="P29" s="131"/>
+      <c r="Q29" s="131"/>
+      <c r="R29" s="131"/>
+      <c r="S29" s="131"/>
+      <c r="T29" s="132"/>
     </row>
     <row r="30" spans="1:20" ht="24" customHeight="1">
-      <c r="A30" s="44"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="46"/>
+      <c r="A30" s="130"/>
+      <c r="B30" s="131"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="131"/>
+      <c r="N30" s="131"/>
+      <c r="O30" s="131"/>
+      <c r="P30" s="131"/>
+      <c r="Q30" s="131"/>
+      <c r="R30" s="131"/>
+      <c r="S30" s="131"/>
+      <c r="T30" s="132"/>
     </row>
     <row r="31" spans="1:20" ht="24" customHeight="1">
-      <c r="A31" s="44"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="46"/>
+      <c r="A31" s="130"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="131"/>
+      <c r="L31" s="131"/>
+      <c r="M31" s="131"/>
+      <c r="N31" s="131"/>
+      <c r="O31" s="131"/>
+      <c r="P31" s="131"/>
+      <c r="Q31" s="131"/>
+      <c r="R31" s="131"/>
+      <c r="S31" s="131"/>
+      <c r="T31" s="132"/>
     </row>
     <row r="32" spans="1:20" ht="24" customHeight="1">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="46"/>
+      <c r="A32" s="130"/>
+      <c r="B32" s="131"/>
+      <c r="C32" s="131"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="131"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="131"/>
+      <c r="L32" s="131"/>
+      <c r="M32" s="131"/>
+      <c r="N32" s="131"/>
+      <c r="O32" s="131"/>
+      <c r="P32" s="131"/>
+      <c r="Q32" s="131"/>
+      <c r="R32" s="131"/>
+      <c r="S32" s="131"/>
+      <c r="T32" s="132"/>
     </row>
     <row r="33" spans="1:20" ht="24" customHeight="1">
-      <c r="A33" s="44"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="46"/>
+      <c r="A33" s="130"/>
+      <c r="B33" s="131"/>
+      <c r="C33" s="131"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="131"/>
+      <c r="J33" s="131"/>
+      <c r="K33" s="131"/>
+      <c r="L33" s="131"/>
+      <c r="M33" s="131"/>
+      <c r="N33" s="131"/>
+      <c r="O33" s="131"/>
+      <c r="P33" s="131"/>
+      <c r="Q33" s="131"/>
+      <c r="R33" s="131"/>
+      <c r="S33" s="131"/>
+      <c r="T33" s="132"/>
     </row>
     <row r="34" spans="1:20" ht="24" customHeight="1">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="46"/>
+      <c r="A34" s="130"/>
+      <c r="B34" s="131"/>
+      <c r="C34" s="131"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
+      <c r="J34" s="131"/>
+      <c r="K34" s="131"/>
+      <c r="L34" s="131"/>
+      <c r="M34" s="131"/>
+      <c r="N34" s="131"/>
+      <c r="O34" s="131"/>
+      <c r="P34" s="131"/>
+      <c r="Q34" s="131"/>
+      <c r="R34" s="131"/>
+      <c r="S34" s="131"/>
+      <c r="T34" s="132"/>
     </row>
     <row r="35" spans="1:20" ht="24" customHeight="1" thickBot="1">
-      <c r="A35" s="49"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="51"/>
+      <c r="A35" s="135"/>
+      <c r="B35" s="136"/>
+      <c r="C35" s="136"/>
+      <c r="D35" s="136"/>
+      <c r="E35" s="136"/>
+      <c r="F35" s="136"/>
+      <c r="G35" s="136"/>
+      <c r="H35" s="136"/>
+      <c r="I35" s="136"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="136"/>
+      <c r="L35" s="136"/>
+      <c r="M35" s="136"/>
+      <c r="N35" s="136"/>
+      <c r="O35" s="136"/>
+      <c r="P35" s="136"/>
+      <c r="Q35" s="136"/>
+      <c r="R35" s="136"/>
+      <c r="S35" s="136"/>
+      <c r="T35" s="137"/>
     </row>
     <row r="36" spans="1:20" ht="5.25" customHeight="1">
       <c r="A36" s="3"/>
@@ -3533,19 +3534,19 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
-      <c r="L37" s="33" t="s">
+      <c r="L37" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="33" t="s">
+      <c r="M37" s="141"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="141"/>
+      <c r="P37" s="141"/>
+      <c r="Q37" s="142"/>
+      <c r="R37" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="S37" s="34"/>
-      <c r="T37" s="35"/>
+      <c r="S37" s="141"/>
+      <c r="T37" s="142"/>
     </row>
     <row r="38" spans="1:20" ht="18" customHeight="1">
       <c r="A38" s="28" t="s">
@@ -3561,15 +3562,15 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="36"/>
-      <c r="N38" s="36"/>
-      <c r="O38" s="36"/>
-      <c r="P38" s="36"/>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="36"/>
-      <c r="S38" s="36"/>
-      <c r="T38" s="36"/>
+      <c r="L38" s="143"/>
+      <c r="M38" s="143"/>
+      <c r="N38" s="143"/>
+      <c r="O38" s="143"/>
+      <c r="P38" s="143"/>
+      <c r="Q38" s="143"/>
+      <c r="R38" s="143"/>
+      <c r="S38" s="143"/>
+      <c r="T38" s="143"/>
     </row>
     <row r="39" spans="1:20" ht="18" customHeight="1">
       <c r="A39" s="4" t="s">
@@ -3585,15 +3586,15 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="36"/>
-      <c r="R39" s="36"/>
-      <c r="S39" s="36"/>
-      <c r="T39" s="36"/>
+      <c r="L39" s="143"/>
+      <c r="M39" s="143"/>
+      <c r="N39" s="143"/>
+      <c r="O39" s="143"/>
+      <c r="P39" s="143"/>
+      <c r="Q39" s="143"/>
+      <c r="R39" s="143"/>
+      <c r="S39" s="143"/>
+      <c r="T39" s="143"/>
     </row>
     <row r="40" spans="1:20" ht="18" customHeight="1">
       <c r="A40" s="28" t="s">
@@ -3609,15 +3610,15 @@
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="36"/>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="36"/>
-      <c r="S40" s="36"/>
-      <c r="T40" s="36"/>
+      <c r="L40" s="143"/>
+      <c r="M40" s="143"/>
+      <c r="N40" s="143"/>
+      <c r="O40" s="143"/>
+      <c r="P40" s="143"/>
+      <c r="Q40" s="143"/>
+      <c r="R40" s="143"/>
+      <c r="S40" s="143"/>
+      <c r="T40" s="143"/>
     </row>
     <row r="41" spans="1:20" ht="18" customHeight="1">
       <c r="A41" s="29" t="s">
@@ -3674,21 +3675,37 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="D3:E4"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="D5:J6"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="L37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="L38:N40"/>
+    <mergeCell ref="O38:Q40"/>
+    <mergeCell ref="R38:T40"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A20:T35"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C16:T16"/>
+    <mergeCell ref="A17:T17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:T14"/>
+    <mergeCell ref="S10:T11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C13:T13"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="S8:T9"/>
     <mergeCell ref="A9:J11"/>
@@ -3705,37 +3722,21 @@
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
-    <mergeCell ref="S10:T11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C13:T13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C16:T16"/>
-    <mergeCell ref="A17:T17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:T14"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A20:T35"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="L37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="L38:N40"/>
-    <mergeCell ref="O38:Q40"/>
-    <mergeCell ref="R38:T40"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:J6"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D3:E4"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/通勤経路届（その他利用）2020.xlsx
+++ b/通勤経路届（その他利用）2020.xlsx
@@ -1521,10 +1521,247 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1534,33 +1771,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1611,247 +1821,37 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -2574,7 +2574,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2591,28 +2591,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="33">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
     </row>
     <row r="2" spans="1:31" ht="9.75" customHeight="1" thickBot="1">
       <c r="A2" s="2"/>
@@ -2637,28 +2637,28 @@
       <c r="T2" s="3"/>
     </row>
     <row r="3" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="45">
+      <c r="B3" s="115"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="142">
         <v>2020</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="115"/>
+      <c r="F3" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="138">
         <v>4</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="41">
-        <v>1</v>
-      </c>
-      <c r="J3" s="43" t="s">
+      <c r="I3" s="138">
+        <v>27</v>
+      </c>
+      <c r="J3" s="140" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="3"/>
@@ -2674,29 +2674,29 @@
         <v>3</v>
       </c>
       <c r="Q3" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S3" s="7">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="6" customHeight="1" thickBot="1">
-      <c r="A4" s="38"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="44"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="141"/>
       <c r="K4" s="3"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -2709,46 +2709,46 @@
       <c r="T4" s="3"/>
     </row>
     <row r="5" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="50">
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="120">
         <v>201087</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="54" t="s">
+      <c r="L5" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55" t="s">
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="125"/>
     </row>
     <row r="6" spans="1:31" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A6" s="47"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="A6" s="117"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="123"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="10"/>
@@ -2761,165 +2761,165 @@
       <c r="T6" s="9"/>
     </row>
     <row r="7" spans="1:31" ht="18" customHeight="1">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="59" t="s">
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="129" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="59" t="s">
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="129" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="62"/>
+      <c r="R7" s="130"/>
+      <c r="S7" s="130"/>
+      <c r="T7" s="132"/>
     </row>
     <row r="8" spans="1:31" ht="19.5" customHeight="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="87" t="s">
+      <c r="B8" s="111"/>
+      <c r="C8" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="65" t="s">
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="90" t="s">
         <v>13</v>
       </c>
       <c r="M8" s="3"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="65" t="s">
+      <c r="N8" s="90"/>
+      <c r="O8" s="90" t="s">
         <v>2</v>
       </c>
       <c r="P8" s="12"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="66"/>
+      <c r="Q8" s="89"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="91"/>
     </row>
     <row r="9" spans="1:31" ht="12" customHeight="1">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="65"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="90"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="65"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="90"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="64"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="66"/>
+      <c r="Q9" s="89"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="91"/>
     </row>
     <row r="10" spans="1:31" ht="12" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="73">
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="98">
         <v>5</v>
       </c>
-      <c r="L10" s="75" t="s">
+      <c r="L10" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="77">
+      <c r="M10" s="102">
         <v>8</v>
       </c>
-      <c r="N10" s="75" t="s">
+      <c r="N10" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="77">
+      <c r="O10" s="102">
         <v>24</v>
       </c>
-      <c r="P10" s="79" t="s">
+      <c r="P10" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="81" t="s">
+      <c r="Q10" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="82"/>
-      <c r="S10" s="89" t="s">
+      <c r="R10" s="107"/>
+      <c r="S10" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="90"/>
+      <c r="T10" s="81"/>
     </row>
     <row r="11" spans="1:31" ht="12" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="76"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="80"/>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="84"/>
-      <c r="S11" s="91"/>
-      <c r="T11" s="92"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="105"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="83"/>
     </row>
     <row r="12" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="84" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="95">
+      <c r="C12" s="86">
         <v>616</v>
       </c>
-      <c r="D12" s="95"/>
+      <c r="D12" s="86"/>
       <c r="E12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="86">
         <v>8137</v>
       </c>
-      <c r="G12" s="95"/>
+      <c r="G12" s="86"/>
       <c r="H12" s="15"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -2935,80 +2935,80 @@
       <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A13" s="94"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="96" t="s">
+      <c r="C13" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="97"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="87"/>
+      <c r="M13" s="87"/>
+      <c r="N13" s="87"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="88"/>
     </row>
     <row r="14" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A14" s="112" t="s">
+      <c r="A14" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="115" t="s">
+      <c r="B14" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="116"/>
-      <c r="D14" s="117" t="s">
+      <c r="C14" s="73"/>
+      <c r="D14" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="115" t="s">
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="120" t="s">
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="121"/>
-      <c r="Q14" s="121"/>
-      <c r="R14" s="121"/>
-      <c r="S14" s="121"/>
-      <c r="T14" s="122"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="79"/>
       <c r="AE14" s="19"/>
     </row>
     <row r="15" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A15" s="113"/>
+      <c r="A15" s="70"/>
       <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="98">
+      <c r="C15" s="55">
         <v>601</v>
       </c>
-      <c r="D15" s="98"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="98">
+      <c r="F15" s="55">
         <v>8319</v>
       </c>
-      <c r="G15" s="98"/>
+      <c r="G15" s="55"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -3025,83 +3025,83 @@
       <c r="AE15" s="19"/>
     </row>
     <row r="16" spans="1:31" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A16" s="114"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="99" t="s">
+      <c r="C16" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="99"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="99"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="99"/>
-      <c r="O16" s="99"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="99"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="100"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="57"/>
     </row>
     <row r="17" spans="1:20" ht="18.95" customHeight="1">
-      <c r="A17" s="101" t="s">
+      <c r="A17" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="102"/>
-      <c r="E17" s="102"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="102"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="102"/>
-      <c r="K17" s="102"/>
-      <c r="L17" s="102"/>
-      <c r="M17" s="102"/>
-      <c r="N17" s="102"/>
-      <c r="O17" s="103"/>
-      <c r="P17" s="103"/>
-      <c r="Q17" s="103"/>
-      <c r="R17" s="103"/>
-      <c r="S17" s="103"/>
-      <c r="T17" s="104"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="61"/>
     </row>
     <row r="18" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="106"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="107" t="s">
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="108"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="110">
+      <c r="F18" s="65"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="67">
         <v>5.2</v>
       </c>
-      <c r="I18" s="111"/>
+      <c r="I18" s="68"/>
       <c r="J18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="107" t="s">
+      <c r="K18" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="108"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="110">
+      <c r="L18" s="65"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="67">
         <v>10.4</v>
       </c>
-      <c r="O18" s="111"/>
+      <c r="O18" s="68"/>
       <c r="P18" s="23" t="s">
         <v>28</v>
       </c>
@@ -3111,392 +3111,392 @@
       <c r="T18" s="25"/>
     </row>
     <row r="19" spans="1:20" ht="23.1" customHeight="1">
-      <c r="A19" s="139" t="s">
+      <c r="A19" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="64"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="26"/>
-      <c r="D19" s="123" t="s">
+      <c r="D19" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="123"/>
-      <c r="F19" s="124"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
       <c r="G19" s="26"/>
-      <c r="H19" s="123" t="s">
+      <c r="H19" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="123"/>
-      <c r="J19" s="124"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="38"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="125" t="s">
+      <c r="L19" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="125"/>
+      <c r="M19" s="39"/>
       <c r="N19" s="26"/>
-      <c r="O19" s="125" t="s">
+      <c r="O19" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="P19" s="126"/>
+      <c r="P19" s="40"/>
       <c r="Q19" s="9"/>
-      <c r="R19" s="125" t="s">
+      <c r="R19" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="S19" s="125"/>
-      <c r="T19" s="138"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="52"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="128"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="128"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="128"/>
-      <c r="L20" s="128"/>
-      <c r="M20" s="128"/>
-      <c r="N20" s="128"/>
-      <c r="O20" s="128"/>
-      <c r="P20" s="128"/>
-      <c r="Q20" s="128"/>
-      <c r="R20" s="128"/>
-      <c r="S20" s="128"/>
-      <c r="T20" s="129"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="43"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1">
-      <c r="A21" s="130"/>
-      <c r="B21" s="131"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="131"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="131"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="131"/>
-      <c r="Q21" s="131"/>
-      <c r="R21" s="131"/>
-      <c r="S21" s="131"/>
-      <c r="T21" s="132"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="46"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1">
-      <c r="A22" s="130"/>
-      <c r="B22" s="131"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="131"/>
-      <c r="L22" s="131"/>
-      <c r="M22" s="131"/>
-      <c r="N22" s="131"/>
-      <c r="O22" s="131"/>
-      <c r="P22" s="131"/>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="131"/>
-      <c r="S22" s="131"/>
-      <c r="T22" s="132"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="45"/>
+      <c r="S22" s="45"/>
+      <c r="T22" s="46"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1">
-      <c r="A23" s="130"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="131"/>
-      <c r="I23" s="131"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="131"/>
-      <c r="L23" s="131"/>
-      <c r="M23" s="131"/>
-      <c r="N23" s="131"/>
-      <c r="O23" s="131"/>
-      <c r="P23" s="131"/>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="131"/>
-      <c r="S23" s="131"/>
-      <c r="T23" s="132"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="46"/>
     </row>
     <row r="24" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A24" s="130"/>
-      <c r="B24" s="131"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="131"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="131"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="131"/>
-      <c r="L24" s="131"/>
-      <c r="M24" s="131"/>
-      <c r="N24" s="131"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="131"/>
-      <c r="Q24" s="131"/>
-      <c r="R24" s="131"/>
-      <c r="S24" s="131"/>
-      <c r="T24" s="132"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="46"/>
     </row>
     <row r="25" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A25" s="130"/>
-      <c r="B25" s="131"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="131"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="131"/>
-      <c r="J25" s="131"/>
-      <c r="K25" s="131"/>
-      <c r="L25" s="131"/>
-      <c r="M25" s="131"/>
-      <c r="N25" s="131"/>
-      <c r="O25" s="131"/>
-      <c r="P25" s="131"/>
-      <c r="Q25" s="131"/>
-      <c r="R25" s="131"/>
-      <c r="S25" s="131"/>
-      <c r="T25" s="132"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="45"/>
+      <c r="R25" s="45"/>
+      <c r="S25" s="45"/>
+      <c r="T25" s="46"/>
     </row>
     <row r="26" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A26" s="130"/>
-      <c r="B26" s="131"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="131"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="131"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
-      <c r="J26" s="131"/>
-      <c r="K26" s="131"/>
-      <c r="L26" s="131"/>
-      <c r="M26" s="131"/>
-      <c r="N26" s="131"/>
-      <c r="O26" s="131"/>
-      <c r="P26" s="131"/>
-      <c r="Q26" s="131"/>
-      <c r="R26" s="131"/>
-      <c r="S26" s="131"/>
-      <c r="T26" s="132"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="46"/>
     </row>
     <row r="27" spans="1:20" ht="24" customHeight="1">
-      <c r="A27" s="133"/>
-      <c r="B27" s="131"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="134"/>
-      <c r="L27" s="131"/>
-      <c r="M27" s="131"/>
-      <c r="N27" s="131"/>
-      <c r="O27" s="131"/>
-      <c r="P27" s="131"/>
-      <c r="Q27" s="131"/>
-      <c r="R27" s="131"/>
-      <c r="S27" s="131"/>
-      <c r="T27" s="132"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="45"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="46"/>
     </row>
     <row r="28" spans="1:20" ht="24" customHeight="1">
-      <c r="A28" s="130"/>
-      <c r="B28" s="131"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="131"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="131"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="131"/>
-      <c r="L28" s="131"/>
-      <c r="M28" s="131"/>
-      <c r="N28" s="131"/>
-      <c r="O28" s="131"/>
-      <c r="P28" s="131"/>
-      <c r="Q28" s="131"/>
-      <c r="R28" s="131"/>
-      <c r="S28" s="131"/>
-      <c r="T28" s="132"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="46"/>
     </row>
     <row r="29" spans="1:20" ht="24" customHeight="1">
-      <c r="A29" s="130"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="131"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="131"/>
-      <c r="L29" s="131"/>
-      <c r="M29" s="131"/>
-      <c r="N29" s="131"/>
-      <c r="O29" s="131"/>
-      <c r="P29" s="131"/>
-      <c r="Q29" s="131"/>
-      <c r="R29" s="131"/>
-      <c r="S29" s="131"/>
-      <c r="T29" s="132"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="45"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="45"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="46"/>
     </row>
     <row r="30" spans="1:20" ht="24" customHeight="1">
-      <c r="A30" s="130"/>
-      <c r="B30" s="131"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="131"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="131"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="131"/>
-      <c r="L30" s="131"/>
-      <c r="M30" s="131"/>
-      <c r="N30" s="131"/>
-      <c r="O30" s="131"/>
-      <c r="P30" s="131"/>
-      <c r="Q30" s="131"/>
-      <c r="R30" s="131"/>
-      <c r="S30" s="131"/>
-      <c r="T30" s="132"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="46"/>
     </row>
     <row r="31" spans="1:20" ht="24" customHeight="1">
-      <c r="A31" s="130"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="131"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="131"/>
-      <c r="L31" s="131"/>
-      <c r="M31" s="131"/>
-      <c r="N31" s="131"/>
-      <c r="O31" s="131"/>
-      <c r="P31" s="131"/>
-      <c r="Q31" s="131"/>
-      <c r="R31" s="131"/>
-      <c r="S31" s="131"/>
-      <c r="T31" s="132"/>
+      <c r="A31" s="44"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="45"/>
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="46"/>
     </row>
     <row r="32" spans="1:20" ht="24" customHeight="1">
-      <c r="A32" s="130"/>
-      <c r="B32" s="131"/>
-      <c r="C32" s="131"/>
-      <c r="D32" s="131"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="131"/>
-      <c r="G32" s="131"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
-      <c r="J32" s="131"/>
-      <c r="K32" s="131"/>
-      <c r="L32" s="131"/>
-      <c r="M32" s="131"/>
-      <c r="N32" s="131"/>
-      <c r="O32" s="131"/>
-      <c r="P32" s="131"/>
-      <c r="Q32" s="131"/>
-      <c r="R32" s="131"/>
-      <c r="S32" s="131"/>
-      <c r="T32" s="132"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="45"/>
+      <c r="P32" s="45"/>
+      <c r="Q32" s="45"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="46"/>
     </row>
     <row r="33" spans="1:20" ht="24" customHeight="1">
-      <c r="A33" s="130"/>
-      <c r="B33" s="131"/>
-      <c r="C33" s="131"/>
-      <c r="D33" s="131"/>
-      <c r="E33" s="131"/>
-      <c r="F33" s="131"/>
-      <c r="G33" s="131"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="131"/>
-      <c r="J33" s="131"/>
-      <c r="K33" s="131"/>
-      <c r="L33" s="131"/>
-      <c r="M33" s="131"/>
-      <c r="N33" s="131"/>
-      <c r="O33" s="131"/>
-      <c r="P33" s="131"/>
-      <c r="Q33" s="131"/>
-      <c r="R33" s="131"/>
-      <c r="S33" s="131"/>
-      <c r="T33" s="132"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="45"/>
+      <c r="P33" s="45"/>
+      <c r="Q33" s="45"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="46"/>
     </row>
     <row r="34" spans="1:20" ht="24" customHeight="1">
-      <c r="A34" s="130"/>
-      <c r="B34" s="131"/>
-      <c r="C34" s="131"/>
-      <c r="D34" s="131"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="131"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="131"/>
-      <c r="J34" s="131"/>
-      <c r="K34" s="131"/>
-      <c r="L34" s="131"/>
-      <c r="M34" s="131"/>
-      <c r="N34" s="131"/>
-      <c r="O34" s="131"/>
-      <c r="P34" s="131"/>
-      <c r="Q34" s="131"/>
-      <c r="R34" s="131"/>
-      <c r="S34" s="131"/>
-      <c r="T34" s="132"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="45"/>
+      <c r="P34" s="45"/>
+      <c r="Q34" s="45"/>
+      <c r="R34" s="45"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="46"/>
     </row>
     <row r="35" spans="1:20" ht="24" customHeight="1" thickBot="1">
-      <c r="A35" s="135"/>
-      <c r="B35" s="136"/>
-      <c r="C35" s="136"/>
-      <c r="D35" s="136"/>
-      <c r="E35" s="136"/>
-      <c r="F35" s="136"/>
-      <c r="G35" s="136"/>
-      <c r="H35" s="136"/>
-      <c r="I35" s="136"/>
-      <c r="J35" s="136"/>
-      <c r="K35" s="136"/>
-      <c r="L35" s="136"/>
-      <c r="M35" s="136"/>
-      <c r="N35" s="136"/>
-      <c r="O35" s="136"/>
-      <c r="P35" s="136"/>
-      <c r="Q35" s="136"/>
-      <c r="R35" s="136"/>
-      <c r="S35" s="136"/>
-      <c r="T35" s="137"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="50"/>
+      <c r="T35" s="51"/>
     </row>
     <row r="36" spans="1:20" ht="5.25" customHeight="1">
       <c r="A36" s="3"/>
@@ -3534,19 +3534,19 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
-      <c r="L37" s="140" t="s">
+      <c r="L37" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="141"/>
-      <c r="N37" s="141"/>
-      <c r="O37" s="141"/>
-      <c r="P37" s="141"/>
-      <c r="Q37" s="142"/>
-      <c r="R37" s="140" t="s">
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="S37" s="141"/>
-      <c r="T37" s="142"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="35"/>
     </row>
     <row r="38" spans="1:20" ht="18" customHeight="1">
       <c r="A38" s="28" t="s">
@@ -3562,15 +3562,15 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="143"/>
-      <c r="M38" s="143"/>
-      <c r="N38" s="143"/>
-      <c r="O38" s="143"/>
-      <c r="P38" s="143"/>
-      <c r="Q38" s="143"/>
-      <c r="R38" s="143"/>
-      <c r="S38" s="143"/>
-      <c r="T38" s="143"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
     </row>
     <row r="39" spans="1:20" ht="18" customHeight="1">
       <c r="A39" s="4" t="s">
@@ -3586,15 +3586,15 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="143"/>
-      <c r="M39" s="143"/>
-      <c r="N39" s="143"/>
-      <c r="O39" s="143"/>
-      <c r="P39" s="143"/>
-      <c r="Q39" s="143"/>
-      <c r="R39" s="143"/>
-      <c r="S39" s="143"/>
-      <c r="T39" s="143"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
     </row>
     <row r="40" spans="1:20" ht="18" customHeight="1">
       <c r="A40" s="28" t="s">
@@ -3610,15 +3610,15 @@
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
-      <c r="L40" s="143"/>
-      <c r="M40" s="143"/>
-      <c r="N40" s="143"/>
-      <c r="O40" s="143"/>
-      <c r="P40" s="143"/>
-      <c r="Q40" s="143"/>
-      <c r="R40" s="143"/>
-      <c r="S40" s="143"/>
-      <c r="T40" s="143"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
     </row>
     <row r="41" spans="1:20" ht="18" customHeight="1">
       <c r="A41" s="29" t="s">
@@ -3675,37 +3675,21 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="L37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="L38:N40"/>
-    <mergeCell ref="O38:Q40"/>
-    <mergeCell ref="R38:T40"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A20:T35"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C16:T16"/>
-    <mergeCell ref="A17:T17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:T14"/>
-    <mergeCell ref="S10:T11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C13:T13"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D3:E4"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:J6"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="Q7:T7"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="S8:T9"/>
     <mergeCell ref="A9:J11"/>
@@ -3722,21 +3706,37 @@
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="D5:J6"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="D3:E4"/>
+    <mergeCell ref="S10:T11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C13:T13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C16:T16"/>
+    <mergeCell ref="A17:T17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:T14"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A20:T35"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="L37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="L38:N40"/>
+    <mergeCell ref="O38:Q40"/>
+    <mergeCell ref="R38:T40"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/通勤経路届（その他利用）2020.xlsx
+++ b/通勤経路届（その他利用）2020.xlsx
@@ -1521,17 +1521,275 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -1584,274 +1842,16 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -2574,7 +2574,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2591,28 +2591,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="33">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
     </row>
     <row r="2" spans="1:31" ht="9.75" customHeight="1" thickBot="1">
       <c r="A2" s="2"/>
@@ -2637,28 +2637,28 @@
       <c r="T2" s="3"/>
     </row>
     <row r="3" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A3" s="114" t="s">
+      <c r="A3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="142">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="45">
         <v>2020</v>
       </c>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="138">
+      <c r="G3" s="41">
+        <v>6</v>
+      </c>
+      <c r="H3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="115" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="138">
-        <v>27</v>
-      </c>
-      <c r="J3" s="140" t="s">
+      <c r="I3" s="41">
+        <v>22</v>
+      </c>
+      <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="3"/>
@@ -2674,29 +2674,29 @@
         <v>3</v>
       </c>
       <c r="Q3" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S3" s="7">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="6" customHeight="1" thickBot="1">
-      <c r="A4" s="135"/>
-      <c r="B4" s="136"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="141"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="3"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -2709,46 +2709,46 @@
       <c r="T4" s="3"/>
     </row>
     <row r="5" spans="1:31" ht="16.5" customHeight="1">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="120">
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="50">
         <v>201087</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="124" t="s">
+      <c r="L5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="125" t="s">
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="125"/>
-      <c r="Q5" s="125"/>
-      <c r="R5" s="125"/>
-      <c r="S5" s="125"/>
-      <c r="T5" s="125"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
     </row>
     <row r="6" spans="1:31" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A6" s="117"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="10"/>
@@ -2761,165 +2761,165 @@
       <c r="T6" s="9"/>
     </row>
     <row r="7" spans="1:31" ht="18" customHeight="1">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="129" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="129" t="s">
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="60"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="132"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="60"/>
+      <c r="T7" s="62"/>
     </row>
     <row r="8" spans="1:31" ht="19.5" customHeight="1">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="112" t="s">
+      <c r="B8" s="86"/>
+      <c r="C8" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="90" t="s">
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="65" t="s">
         <v>13</v>
       </c>
       <c r="M8" s="3"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90" t="s">
+      <c r="N8" s="65"/>
+      <c r="O8" s="65" t="s">
         <v>2</v>
       </c>
       <c r="P8" s="12"/>
-      <c r="Q8" s="89"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="91"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="66"/>
     </row>
     <row r="9" spans="1:31" ht="12" customHeight="1">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="65"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="89"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="91"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="64"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:31" ht="12" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="98">
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="73">
         <v>5</v>
       </c>
-      <c r="L10" s="100" t="s">
+      <c r="L10" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="102">
+      <c r="M10" s="77">
         <v>8</v>
       </c>
-      <c r="N10" s="100" t="s">
+      <c r="N10" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="102">
+      <c r="O10" s="77">
         <v>24</v>
       </c>
-      <c r="P10" s="104" t="s">
+      <c r="P10" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="106" t="s">
+      <c r="Q10" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="107"/>
-      <c r="S10" s="80" t="s">
+      <c r="R10" s="82"/>
+      <c r="S10" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="81"/>
+      <c r="T10" s="90"/>
     </row>
     <row r="11" spans="1:31" ht="12" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="101"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="101"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="109"/>
-      <c r="S11" s="82"/>
-      <c r="T11" s="83"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="76"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="91"/>
+      <c r="T11" s="92"/>
     </row>
     <row r="12" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="93" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="95">
         <v>616</v>
       </c>
-      <c r="D12" s="86"/>
+      <c r="D12" s="95"/>
       <c r="E12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="86">
+      <c r="F12" s="95">
         <v>8137</v>
       </c>
-      <c r="G12" s="86"/>
+      <c r="G12" s="95"/>
       <c r="H12" s="15"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -2935,80 +2935,80 @@
       <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A13" s="85"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="87"/>
-      <c r="L13" s="87"/>
-      <c r="M13" s="87"/>
-      <c r="N13" s="87"/>
-      <c r="O13" s="87"/>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="87"/>
-      <c r="S13" s="87"/>
-      <c r="T13" s="88"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="96"/>
+      <c r="T13" s="97"/>
     </row>
     <row r="14" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74" t="s">
+      <c r="C14" s="116"/>
+      <c r="D14" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="72" t="s">
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="77" t="s">
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="79"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="121"/>
+      <c r="R14" s="121"/>
+      <c r="S14" s="121"/>
+      <c r="T14" s="122"/>
       <c r="AE14" s="19"/>
     </row>
     <row r="15" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A15" s="70"/>
+      <c r="A15" s="113"/>
       <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="98">
         <v>601</v>
       </c>
-      <c r="D15" s="55"/>
+      <c r="D15" s="98"/>
       <c r="E15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="98">
         <v>8319</v>
       </c>
-      <c r="G15" s="55"/>
+      <c r="G15" s="98"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -3025,83 +3025,83 @@
       <c r="AE15" s="19"/>
     </row>
     <row r="16" spans="1:31" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A16" s="71"/>
+      <c r="A16" s="114"/>
       <c r="B16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="56"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="56"/>
-      <c r="T16" s="57"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="99"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="100"/>
     </row>
     <row r="17" spans="1:20" ht="18.95" customHeight="1">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="61"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="102"/>
+      <c r="L17" s="102"/>
+      <c r="M17" s="102"/>
+      <c r="N17" s="102"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="103"/>
+      <c r="Q17" s="103"/>
+      <c r="R17" s="103"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="104"/>
     </row>
     <row r="18" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="64" t="s">
+      <c r="B18" s="106"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="67">
+      <c r="F18" s="108"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="110">
         <v>5.2</v>
       </c>
-      <c r="I18" s="68"/>
+      <c r="I18" s="111"/>
       <c r="J18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="64" t="s">
+      <c r="K18" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="65"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="67">
+      <c r="L18" s="108"/>
+      <c r="M18" s="109"/>
+      <c r="N18" s="110">
         <v>10.4</v>
       </c>
-      <c r="O18" s="68"/>
+      <c r="O18" s="111"/>
       <c r="P18" s="23" t="s">
         <v>28</v>
       </c>
@@ -3111,392 +3111,392 @@
       <c r="T18" s="25"/>
     </row>
     <row r="19" spans="1:20" ht="23.1" customHeight="1">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="139" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="54"/>
+      <c r="B19" s="64"/>
       <c r="C19" s="26"/>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="38"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="124"/>
       <c r="G19" s="26"/>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="37"/>
-      <c r="J19" s="38"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="124"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="125"/>
       <c r="N19" s="26"/>
-      <c r="O19" s="39" t="s">
+      <c r="O19" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="P19" s="40"/>
+      <c r="P19" s="126"/>
       <c r="Q19" s="9"/>
-      <c r="R19" s="39" t="s">
+      <c r="R19" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="S19" s="39"/>
-      <c r="T19" s="52"/>
+      <c r="S19" s="125"/>
+      <c r="T19" s="138"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="43"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="128"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="128"/>
+      <c r="O20" s="128"/>
+      <c r="P20" s="128"/>
+      <c r="Q20" s="128"/>
+      <c r="R20" s="128"/>
+      <c r="S20" s="128"/>
+      <c r="T20" s="129"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="46"/>
+      <c r="A21" s="130"/>
+      <c r="B21" s="131"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="131"/>
+      <c r="T21" s="132"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1">
-      <c r="A22" s="44"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="46"/>
+      <c r="A22" s="130"/>
+      <c r="B22" s="131"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
+      <c r="M22" s="131"/>
+      <c r="N22" s="131"/>
+      <c r="O22" s="131"/>
+      <c r="P22" s="131"/>
+      <c r="Q22" s="131"/>
+      <c r="R22" s="131"/>
+      <c r="S22" s="131"/>
+      <c r="T22" s="132"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="46"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="131"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="131"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
+      <c r="M23" s="131"/>
+      <c r="N23" s="131"/>
+      <c r="O23" s="131"/>
+      <c r="P23" s="131"/>
+      <c r="Q23" s="131"/>
+      <c r="R23" s="131"/>
+      <c r="S23" s="131"/>
+      <c r="T23" s="132"/>
     </row>
     <row r="24" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="46"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="131"/>
+      <c r="Q24" s="131"/>
+      <c r="R24" s="131"/>
+      <c r="S24" s="131"/>
+      <c r="T24" s="132"/>
     </row>
     <row r="25" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="46"/>
+      <c r="A25" s="130"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="131"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="131"/>
+      <c r="L25" s="131"/>
+      <c r="M25" s="131"/>
+      <c r="N25" s="131"/>
+      <c r="O25" s="131"/>
+      <c r="P25" s="131"/>
+      <c r="Q25" s="131"/>
+      <c r="R25" s="131"/>
+      <c r="S25" s="131"/>
+      <c r="T25" s="132"/>
     </row>
     <row r="26" spans="1:20" ht="21.95" customHeight="1">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="46"/>
+      <c r="A26" s="130"/>
+      <c r="B26" s="131"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="131"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="131"/>
+      <c r="L26" s="131"/>
+      <c r="M26" s="131"/>
+      <c r="N26" s="131"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="131"/>
+      <c r="Q26" s="131"/>
+      <c r="R26" s="131"/>
+      <c r="S26" s="131"/>
+      <c r="T26" s="132"/>
     </row>
     <row r="27" spans="1:20" ht="24" customHeight="1">
-      <c r="A27" s="47"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="46"/>
+      <c r="A27" s="133"/>
+      <c r="B27" s="131"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="134"/>
+      <c r="L27" s="131"/>
+      <c r="M27" s="131"/>
+      <c r="N27" s="131"/>
+      <c r="O27" s="131"/>
+      <c r="P27" s="131"/>
+      <c r="Q27" s="131"/>
+      <c r="R27" s="131"/>
+      <c r="S27" s="131"/>
+      <c r="T27" s="132"/>
     </row>
     <row r="28" spans="1:20" ht="24" customHeight="1">
-      <c r="A28" s="44"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="46"/>
+      <c r="A28" s="130"/>
+      <c r="B28" s="131"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="131"/>
+      <c r="N28" s="131"/>
+      <c r="O28" s="131"/>
+      <c r="P28" s="131"/>
+      <c r="Q28" s="131"/>
+      <c r="R28" s="131"/>
+      <c r="S28" s="131"/>
+      <c r="T28" s="132"/>
     </row>
     <row r="29" spans="1:20" ht="24" customHeight="1">
-      <c r="A29" s="44"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="46"/>
+      <c r="A29" s="130"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
+      <c r="L29" s="131"/>
+      <c r="M29" s="131"/>
+      <c r="N29" s="131"/>
+      <c r="O29" s="131"/>
+      <c r="P29" s="131"/>
+      <c r="Q29" s="131"/>
+      <c r="R29" s="131"/>
+      <c r="S29" s="131"/>
+      <c r="T29" s="132"/>
     </row>
     <row r="30" spans="1:20" ht="24" customHeight="1">
-      <c r="A30" s="44"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="46"/>
+      <c r="A30" s="130"/>
+      <c r="B30" s="131"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="131"/>
+      <c r="N30" s="131"/>
+      <c r="O30" s="131"/>
+      <c r="P30" s="131"/>
+      <c r="Q30" s="131"/>
+      <c r="R30" s="131"/>
+      <c r="S30" s="131"/>
+      <c r="T30" s="132"/>
     </row>
     <row r="31" spans="1:20" ht="24" customHeight="1">
-      <c r="A31" s="44"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="46"/>
+      <c r="A31" s="130"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="131"/>
+      <c r="L31" s="131"/>
+      <c r="M31" s="131"/>
+      <c r="N31" s="131"/>
+      <c r="O31" s="131"/>
+      <c r="P31" s="131"/>
+      <c r="Q31" s="131"/>
+      <c r="R31" s="131"/>
+      <c r="S31" s="131"/>
+      <c r="T31" s="132"/>
     </row>
     <row r="32" spans="1:20" ht="24" customHeight="1">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="46"/>
+      <c r="A32" s="130"/>
+      <c r="B32" s="131"/>
+      <c r="C32" s="131"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="131"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="131"/>
+      <c r="L32" s="131"/>
+      <c r="M32" s="131"/>
+      <c r="N32" s="131"/>
+      <c r="O32" s="131"/>
+      <c r="P32" s="131"/>
+      <c r="Q32" s="131"/>
+      <c r="R32" s="131"/>
+      <c r="S32" s="131"/>
+      <c r="T32" s="132"/>
     </row>
     <row r="33" spans="1:20" ht="24" customHeight="1">
-      <c r="A33" s="44"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="46"/>
+      <c r="A33" s="130"/>
+      <c r="B33" s="131"/>
+      <c r="C33" s="131"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="131"/>
+      <c r="J33" s="131"/>
+      <c r="K33" s="131"/>
+      <c r="L33" s="131"/>
+      <c r="M33" s="131"/>
+      <c r="N33" s="131"/>
+      <c r="O33" s="131"/>
+      <c r="P33" s="131"/>
+      <c r="Q33" s="131"/>
+      <c r="R33" s="131"/>
+      <c r="S33" s="131"/>
+      <c r="T33" s="132"/>
     </row>
     <row r="34" spans="1:20" ht="24" customHeight="1">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="46"/>
+      <c r="A34" s="130"/>
+      <c r="B34" s="131"/>
+      <c r="C34" s="131"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
+      <c r="J34" s="131"/>
+      <c r="K34" s="131"/>
+      <c r="L34" s="131"/>
+      <c r="M34" s="131"/>
+      <c r="N34" s="131"/>
+      <c r="O34" s="131"/>
+      <c r="P34" s="131"/>
+      <c r="Q34" s="131"/>
+      <c r="R34" s="131"/>
+      <c r="S34" s="131"/>
+      <c r="T34" s="132"/>
     </row>
     <row r="35" spans="1:20" ht="24" customHeight="1" thickBot="1">
-      <c r="A35" s="49"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="51"/>
+      <c r="A35" s="135"/>
+      <c r="B35" s="136"/>
+      <c r="C35" s="136"/>
+      <c r="D35" s="136"/>
+      <c r="E35" s="136"/>
+      <c r="F35" s="136"/>
+      <c r="G35" s="136"/>
+      <c r="H35" s="136"/>
+      <c r="I35" s="136"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="136"/>
+      <c r="L35" s="136"/>
+      <c r="M35" s="136"/>
+      <c r="N35" s="136"/>
+      <c r="O35" s="136"/>
+      <c r="P35" s="136"/>
+      <c r="Q35" s="136"/>
+      <c r="R35" s="136"/>
+      <c r="S35" s="136"/>
+      <c r="T35" s="137"/>
     </row>
     <row r="36" spans="1:20" ht="5.25" customHeight="1">
       <c r="A36" s="3"/>
@@ -3534,19 +3534,19 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
-      <c r="L37" s="33" t="s">
+      <c r="L37" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="33" t="s">
+      <c r="M37" s="141"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="141"/>
+      <c r="P37" s="141"/>
+      <c r="Q37" s="142"/>
+      <c r="R37" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="S37" s="34"/>
-      <c r="T37" s="35"/>
+      <c r="S37" s="141"/>
+      <c r="T37" s="142"/>
     </row>
     <row r="38" spans="1:20" ht="18" customHeight="1">
       <c r="A38" s="28" t="s">
@@ -3562,15 +3562,15 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="36"/>
-      <c r="N38" s="36"/>
-      <c r="O38" s="36"/>
-      <c r="P38" s="36"/>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="36"/>
-      <c r="S38" s="36"/>
-      <c r="T38" s="36"/>
+      <c r="L38" s="143"/>
+      <c r="M38" s="143"/>
+      <c r="N38" s="143"/>
+      <c r="O38" s="143"/>
+      <c r="P38" s="143"/>
+      <c r="Q38" s="143"/>
+      <c r="R38" s="143"/>
+      <c r="S38" s="143"/>
+      <c r="T38" s="143"/>
     </row>
     <row r="39" spans="1:20" ht="18" customHeight="1">
       <c r="A39" s="4" t="s">
@@ -3586,15 +3586,15 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="36"/>
-      <c r="R39" s="36"/>
-      <c r="S39" s="36"/>
-      <c r="T39" s="36"/>
+      <c r="L39" s="143"/>
+      <c r="M39" s="143"/>
+      <c r="N39" s="143"/>
+      <c r="O39" s="143"/>
+      <c r="P39" s="143"/>
+      <c r="Q39" s="143"/>
+      <c r="R39" s="143"/>
+      <c r="S39" s="143"/>
+      <c r="T39" s="143"/>
     </row>
     <row r="40" spans="1:20" ht="18" customHeight="1">
       <c r="A40" s="28" t="s">
@@ -3610,15 +3610,15 @@
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="36"/>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="36"/>
-      <c r="S40" s="36"/>
-      <c r="T40" s="36"/>
+      <c r="L40" s="143"/>
+      <c r="M40" s="143"/>
+      <c r="N40" s="143"/>
+      <c r="O40" s="143"/>
+      <c r="P40" s="143"/>
+      <c r="Q40" s="143"/>
+      <c r="R40" s="143"/>
+      <c r="S40" s="143"/>
+      <c r="T40" s="143"/>
     </row>
     <row r="41" spans="1:20" ht="18" customHeight="1">
       <c r="A41" s="29" t="s">
@@ -3675,21 +3675,37 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="D3:E4"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="D5:J6"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="L37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="L38:N40"/>
+    <mergeCell ref="O38:Q40"/>
+    <mergeCell ref="R38:T40"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A20:T35"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C16:T16"/>
+    <mergeCell ref="A17:T17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:T14"/>
+    <mergeCell ref="S10:T11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C13:T13"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="S8:T9"/>
     <mergeCell ref="A9:J11"/>
@@ -3706,37 +3722,21 @@
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
-    <mergeCell ref="S10:T11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C13:T13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C16:T16"/>
-    <mergeCell ref="A17:T17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:T14"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A20:T35"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="L37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="L38:N40"/>
-    <mergeCell ref="O38:Q40"/>
-    <mergeCell ref="R38:T40"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:J6"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D3:E4"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
